--- a/CafeTrainAtmega328/SwitchMap.xlsx
+++ b/CafeTrainAtmega328/SwitchMap.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Atmel Studio\7.0\CafeTrainAtmega328\CafeTrainAtmega328\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33461EAA-BEE9-48B2-8C57-1B4CF2786AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B21C51F-0ACB-470A-B06A-9ABBC9DAB40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9D85FE6F-27BC-4E68-B4AF-A6E1816F3DD7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{9D85FE6F-27BC-4E68-B4AF-A6E1816F3DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
@@ -124,7 +125,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -135,6 +136,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -166,9 +173,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -218,18 +225,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7C75B-5E25-47D3-92A2-AB0D8485024B}" name="Таблица1" displayName="Таблица1" ref="A1:I9" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73F7C75B-5E25-47D3-92A2-AB0D8485024B}" name="Таблица1" displayName="Таблица1" ref="A1:I9" totalsRowShown="0" headerRowDxfId="9">
   <autoFilter ref="A1:I9" xr:uid="{73F7C75B-5E25-47D3-92A2-AB0D8485024B}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{4D904FBF-17FC-4B51-9B0C-6BD33B64970F}" name="Столбец1" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{CD22B85A-3F21-4D64-9AD5-78DB10407005}" name="1" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{67040FD4-F8A4-45D8-A329-D3098DC57CD5}" name="2" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{F32C0435-CFCF-4E22-8EE1-6617767606A3}" name="3" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{57A75FF6-C17A-4D80-BBF3-727FE3ABA3D1}" name="4" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{1731EEE2-B606-48BD-B16A-C0E12882375A}" name="5" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{D1C3220C-E2FA-4262-8C30-54028A42D3AA}" name="6" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{645A0DB7-6706-43E1-BA53-A3C4AC51DB6E}" name="7" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{C82F4842-77A6-427A-B095-584A75FAD180}" name="8" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{4D904FBF-17FC-4B51-9B0C-6BD33B64970F}" name="Столбец1" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{CD22B85A-3F21-4D64-9AD5-78DB10407005}" name="1" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{67040FD4-F8A4-45D8-A329-D3098DC57CD5}" name="2" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{F32C0435-CFCF-4E22-8EE1-6617767606A3}" name="3" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{57A75FF6-C17A-4D80-BBF3-727FE3ABA3D1}" name="4" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{1731EEE2-B606-48BD-B16A-C0E12882375A}" name="5" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{D1C3220C-E2FA-4262-8C30-54028A42D3AA}" name="6" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{645A0DB7-6706-43E1-BA53-A3C4AC51DB6E}" name="7" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{C82F4842-77A6-427A-B095-584A75FAD180}" name="8" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -536,335 +543,334 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <f>C3</f>
         <v>1</v>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>1</v>
       </c>
     </row>
@@ -880,7 +886,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ABB663D-45F4-4291-944D-6558A7658342}">
   <sheetPr codeName="Лист2"/>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
@@ -893,7 +899,7 @@
     <col min="9" max="9" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -922,33 +928,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -977,7 +983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1006,7 +1012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1035,7 +1041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1062,10 +1068,469 @@
       </c>
       <c r="I6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>1</v>
+      </c>
+      <c r="L16" s="4">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4">
+        <v>1</v>
+      </c>
+      <c r="N17" s="4">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <v>1</v>
+      </c>
+      <c r="P18" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C25072-E6D7-4182-8C91-7FB8ACED797C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>